--- a/output/pdf_financials_xlsx/NARA.xlsx
+++ b/output/pdf_financials_xlsx/NARA.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.059568</v>
+        <v>3.641827</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.513729</v>
+        <v>2.858318</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.556604</v>
+        <v>1.152511</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.645075</v>
+        <v>3.401451</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-2.059568</v>
+        <v>-3.641827</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.513729</v>
+        <v>-2.858318</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.556604</v>
+        <v>-1.152511</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.645075</v>
+        <v>-3.401451</v>
       </c>
     </row>
     <row r="12">
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002454</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002383</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000205</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-11.994328</v>
+        <v>-11.996782</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.972914</v>
+        <v>-2.975297</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.803848</v>
+        <v>-3.804053</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.431478</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.983215</v>
+        <v>-11.985669</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.960512</v>
+        <v>-2.962895</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.795326</v>
+        <v>-3.795531</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.43085</v>
@@ -1086,7 +1086,7 @@
         <v>0.001307</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.038766</v>
       </c>
     </row>
     <row r="35">
@@ -1124,7 +1124,7 @@
         <v>0.001307</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.038766</v>
       </c>
     </row>
     <row r="37">
@@ -1352,7 +1352,7 @@
         <v>0.004974</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.154727</v>
+        <v>0.115961</v>
       </c>
     </row>
     <row r="49">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">

--- a/output/pdf_financials_xlsx/NARA.xlsx
+++ b/output/pdf_financials_xlsx/NARA.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.029761</v>
+        <v>1.072261</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.979333</v>
+        <v>1.039333</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.532196</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.645075</v>
+        <v>1.658075</v>
       </c>
     </row>
     <row r="8">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006005</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003142</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006005</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003142</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.782546</v>
+        <v>-2.788551</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.568065</v>
+        <v>-1.571207</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.058253</v>
@@ -5074,7 +5074,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.006005</v>
       </c>
@@ -6074,7 +6078,11 @@
           <t>Director’s fees (Note 5)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7262,7 +7270,11 @@
           <t>Director’s fees (Note 6)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -7948,7 +7960,11 @@
           <t>Director’s fees (Note 10)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>0.0425</v>
       </c>
